--- a/results/02_taxa_assemblage/LDA_Method/ModelS_XSupport/tables/confusion_allref.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelS_XSupport/tables/confusion_allref.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Model S (trained on 29 EnvStrong_TaxaStrong sites)</t>
+          <t>Model S (trained on 13 EnvStrong_TaxaStrong sites)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -468,16 +468,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -506,16 +506,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -525,16 +525,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -547,7 +547,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Baseline (trained on all 50 ref sites)</t>
+          <t>Baseline (trained on all 42 ref sites)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -562,16 +562,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -619,16 +619,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="C12" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/LDA_Method/ModelS_XSupport/tables/confusion_allref.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelS_XSupport/tables/confusion_allref.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Model S (trained on 16 EnvStrong_TaxaStrong sites)</t>
+          <t>Model S (trained on 17 EnvStrong_TaxaStrong sites)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -468,16 +468,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -490,7 +490,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -515,7 +515,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -525,16 +525,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -547,7 +547,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Baseline (trained on all 52 ref sites)</t>
+          <t>Baseline (trained on all 59 ref sites)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -562,10 +562,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>4</v>
@@ -619,13 +619,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C12" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>7</v>
